--- a/data/numeric/input/old_data_68/1.xlsx
+++ b/data/numeric/input/old_data_68/1.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/wps1.2/数值统计/input/DLG_225/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/input/old_data_68/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA85DF5-4111-184E-ABF7-11F30BA9268B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{865E1D2B-6544-2445-B4CC-060330658B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A801951-3E25-466B-9FEF-8F414AFC8B0E}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35840" yWindow="1300" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="98">
   <si>
     <t>直播复盘表</t>
   </si>
@@ -41,9 +44,6 @@
     <t>直播日期</t>
   </si>
   <si>
-    <t>2024年8月1日</t>
-  </si>
-  <si>
     <t>直播总时长</t>
   </si>
   <si>
@@ -71,10 +71,19 @@
     <t>框架复盘</t>
   </si>
   <si>
+    <t>A店定播</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>A店</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>夏日泼水氛围</t>
   </si>
   <si>
-    <t>140半价日历票+99夜场票+二销产品（双份雪糕、爆米花桶+常饮杯、双份畅饮杯）</t>
+    <t>日历票+夜场票+产品（爆米花桶、雪糕）</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>——</t>
@@ -101,14 +110,29 @@
     <t>截图</t>
   </si>
   <si>
+    <t>主播1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>运营2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>8:00-9:30</t>
   </si>
   <si>
     <t>6567</t>
   </si>
   <si>
-    <t>1.重复回答
-2.方特旅游不要说下载，看公屏即可，</t>
+    <t>直播要点1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>主播7</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>运营3</t>
   </si>
   <si>
     <t>9:30-11:30</t>
@@ -117,8 +141,13 @@
     <t>32873</t>
   </si>
   <si>
-    <t>1、遇到事情淡定处理，事情处理完后，在线人数上升
-2、暂无大场</t>
+    <t>直播要点2</t>
+  </si>
+  <si>
+    <t>主播3</t>
+  </si>
+  <si>
+    <t>运营4</t>
   </si>
   <si>
     <t>11:30-13:30</t>
@@ -127,7 +156,13 @@
     <t>27385</t>
   </si>
   <si>
-    <t>应变能力稍微差点</t>
+    <t>直播要点3</t>
+  </si>
+  <si>
+    <t>主播4</t>
+  </si>
+  <si>
+    <t>运营5</t>
   </si>
   <si>
     <t>13:30-15:00</t>
@@ -136,7 +171,14 @@
     <t>29616</t>
   </si>
   <si>
-    <t>1.讲解耐心且仔细2.话术有循环</t>
+    <t>直播要点4</t>
+  </si>
+  <si>
+    <t>主播5</t>
+  </si>
+  <si>
+    <t>运营7</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>15:00-17:00</t>
@@ -145,8 +187,14 @@
     <t>31040</t>
   </si>
   <si>
-    <t>1、眼睛盯住摄像头，不要乱飘
-2、后半段有点萎靡</t>
+    <t>直播要点5</t>
+  </si>
+  <si>
+    <t>主播6</t>
+  </si>
+  <si>
+    <t>运营1</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>17:00-19：00</t>
@@ -155,10 +203,11 @@
     <t>20494</t>
   </si>
   <si>
-    <t>1.不要直接说在方特旅游拍年卡 属于站外引流-1
-2.讲解耐心
-3.活动基本清楚
-4.需加强促单-1</t>
+    <t>直播要点6</t>
+  </si>
+  <si>
+    <t>主播2</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>19:00-21:10</t>
@@ -167,7 +216,11 @@
     <t>39746</t>
   </si>
   <si>
-    <t>1.讲解耐心2.优惠券利用的很好3.暂无大场</t>
+    <t>直播要点7</t>
+  </si>
+  <si>
+    <t>运营8</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>21：10-22:10</t>
@@ -176,13 +229,22 @@
     <t>17209</t>
   </si>
   <si>
+    <t>运营6</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>22：10-23:00</t>
   </si>
   <si>
     <t>21712</t>
   </si>
   <si>
-    <t>1.话术有循环2.讲解耐心3.暂无大场</t>
+    <t>直播要点8</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>主播8</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>23:00-23:30</t>
@@ -197,7 +259,8 @@
     <t>8352</t>
   </si>
   <si>
-    <t>1.有固定人设2.讲解耐心，激情3.暂无大场</t>
+    <t>直播要点9</t>
+    <phoneticPr fontId="0" type="noConversion"/>
   </si>
   <si>
     <t>总GMV（元）</t>
@@ -284,71 +347,6 @@
   </si>
   <si>
     <t>曝光转化率</t>
-  </si>
-  <si>
-    <t>A店定播</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>A店</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>主播1</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>主播2</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>主播3</t>
-  </si>
-  <si>
-    <t>主播4</t>
-  </si>
-  <si>
-    <t>主播5</t>
-  </si>
-  <si>
-    <t>主播6</t>
-  </si>
-  <si>
-    <t>主播7</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>主播8</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营1</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营2</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营3</t>
-  </si>
-  <si>
-    <t>运营4</t>
-  </si>
-  <si>
-    <t>运营5</t>
-  </si>
-  <si>
-    <t>运营6</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营7</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>运营8</t>
-    <phoneticPr fontId="0" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -392,9 +390,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -697,196 +696,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="B3:H37"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
+  <cols>
+    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="3" spans="2:8">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+    <row r="4" spans="2:8">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" s="2">
+        <v>45748</v>
+      </c>
+      <c r="F4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row r="6" spans="2:8">
+      <c r="B6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+      <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H6" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="I5" t="e">
-        <f ca="1">DISPIMG("ID_86AE6E45A5C446E89D78DEEDB1892DAA",1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="J5" t="e">
-        <f ca="1">DISPIMG("ID_267DC5A18E1B48A2AF0D871E14B124BE",1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="K5" t="e">
-        <f ca="1">DISPIMG("ID_E4D2067B691D49F0AE5C01E0EAA9D9B2",1)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L5" t="e">
-        <f ca="1">DISPIMG("ID_39DB826CAE264758937EEA262F9878DA",1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
+      <c r="H7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="2:8">
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="H9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="10" spans="2:8">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" t="s">
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="I8" t="e">
-        <f ca="1">DISPIMG("ID_C0DC1BDA1BC34F78946598E857BD72FA",1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E10" t="s">
         <v>25</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F10" t="s">
         <v>26</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G10" t="s">
         <v>27</v>
       </c>
-      <c r="I9" t="e">
-        <f ca="1">DISPIMG("ID_884E4C3846444E27B1595F99EB22B1A8",1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="11" spans="2:8">
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>31</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" t="s">
+    </row>
+    <row r="12" spans="2:8">
+      <c r="C12" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
@@ -897,283 +838,316 @@
       <c r="F12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" t="s">
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="C26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="C27" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" t="s">
         <v>91</v>
       </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14" t="s">
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="C30" t="s">
         <v>84</v>
       </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="B16" t="s">
+      <c r="F30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="C33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="C34" t="s">
         <v>84</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" t="s">
         <v>96</v>
       </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" t="e">
-        <f ca="1">DISPIMG("ID_0DFA553183EF442BAEEFDD1756143A7E",1)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35" t="s">
-        <v>80</v>
+      <c r="H37" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1183,6 +1157,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -1330,29 +1319,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE452720-C341-4119-9150-EE86420E98CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D454864D-7E0E-44C7-9320-B69EAA095AB2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363A7BE5-2DCE-4435-ADE9-69FEEA0EBB3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E52DBC5-BB46-47DE-B21C-6F1764B0ADDE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{446087B0-79EB-4B9B-8E59-6451FF48F3EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F183E739-77BB-4342-9D79-8C79FC07B775}"/>
 </file>